--- a/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8782586bde774c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R089d2c7b01da4d46"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R089d2c7b01da4d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86835b3fe8f64159"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86835b3fe8f64159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R821bb880882d4ff5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R821bb880882d4ff5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96e4e14e44c9466c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96e4e14e44c9466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5705fc6d14b44258"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5705fc6d14b44258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3024db393cd4265"/>
   </x:sheets>
 </x:workbook>
 </file>
